--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post FET_HRM-2031-0372/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.92067</v>
+        <v>17.02115</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52885</v>
+        <v>16.6403</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76518</v>
+        <v>16.67124</v>
       </c>
       <c r="F2" t="n">
-        <v>43.41214</v>
+        <v>42.75207</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05039</v>
+        <v>0.05007</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83163</v>
+        <v>1.83322</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63369</v>
+        <v>16.97459</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47806</v>
+        <v>16.61968</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62364</v>
+        <v>16.82995</v>
       </c>
       <c r="F3" t="n">
-        <v>41.83377</v>
+        <v>42.24629</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0496</v>
+        <v>0.05056</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80592</v>
+        <v>1.83122</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.73527</v>
+        <v>16.73507</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61382</v>
+        <v>16.22609</v>
       </c>
       <c r="E4" t="n">
-        <v>16.53777</v>
+        <v>16.54115</v>
       </c>
       <c r="F4" t="n">
-        <v>42.52002</v>
+        <v>42.38145</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0502</v>
+        <v>0.05087</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81787</v>
+        <v>1.83897</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.67405</v>
+        <v>16.56637</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10041</v>
+        <v>16.06666</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53772</v>
+        <v>16.4041</v>
       </c>
       <c r="F6" t="n">
-        <v>21.54352</v>
+        <v>22.14401</v>
       </c>
       <c r="G6" t="n">
-        <v>34.20836</v>
+        <v>34.70155</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.94259</v>
+        <v>16.46602</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00478</v>
+        <v>16.00299</v>
       </c>
       <c r="E7" t="n">
-        <v>16.74722</v>
+        <v>16.43523</v>
       </c>
       <c r="F7" t="n">
-        <v>21.8054</v>
+        <v>21.30887</v>
       </c>
       <c r="G7" t="n">
-        <v>34.04578</v>
+        <v>34.39101</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.93446</v>
+        <v>16.63246</v>
       </c>
       <c r="D8" t="n">
-        <v>16.07017</v>
+        <v>15.99853</v>
       </c>
       <c r="E8" t="n">
-        <v>16.66038</v>
+        <v>16.47242</v>
       </c>
       <c r="F8" t="n">
-        <v>21.80713</v>
+        <v>21.76631</v>
       </c>
       <c r="G8" t="n">
-        <v>34.38912</v>
+        <v>34.02638</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61233</v>
+        <v>0.61282</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12347</v>
+        <v>1.12602</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60266</v>
+        <v>0.59648</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11433</v>
+        <v>1.11139</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60631</v>
+        <v>0.60967</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13091</v>
+        <v>1.11106</v>
       </c>
     </row>
   </sheetData>
